--- a/tools/note投稿メタ情報.xlsx
+++ b/tools/note投稿メタ情報.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="286">
   <si>
     <t xml:space="preserve">No</t>
   </si>
@@ -7619,7 +7619,37 @@
     <t xml:space="preserve">記事タイトル</t>
   </si>
   <si>
-    <t xml:space="preserve">キャプション（本文＋タグ）</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">キャプション（絵文字・タグ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個込み）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">合計
@@ -7630,7 +7660,7 @@
 字数</t>
   </si>
   <si>
-    <t xml:space="preserve">タグ
+    <t xml:space="preserve">絵文字
 数</t>
   </si>
   <si>
@@ -7640,14 +7670,14 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ダイエット中、お酒だけはやめられない。
+      <t xml:space="preserve">🍺 ダイエット中、お酒だけはやめられない。
 正直なところ、やめなくていいです。
 効くのは量より、終える時刻でした。
 お酒の問題はカロリーじゃなく、処理の順番です。
 アルコールは体にとって異物なので、解毒が割り込みで優先されます。そのあいだ、脂肪を燃やす作業は後回しになります。
 そして「寝つきが良くなる」のは、睡眠の前借りです。夜の後半で切れ切れになり、深い睡眠が減ります。つまり寝つきを買って、整備の時間を売っている状態です。
-ーーーーー
-やることは</t>
+┈┈┈┈┈┈┈┈┈┈
+💡 やることは</t>
     </r>
     <r>
       <rPr>
@@ -7665,8 +7695,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つだけ。
-・飲まない日を週に何日か決める
-・寝る</t>
+✅ 飲まない日を週に何日か決める
+✅ 寝る</t>
     </r>
     <r>
       <rPr>
@@ -7685,10 +7715,10 @@
       </rPr>
       <t xml:space="preserve">時間前に切り上げる
 量は減らさなくていいです。座る前に終える時刻だけ決めてください。
-ーーーーー
-顔が赤くなる人は、同じ量でも体への負担が大きい体質です。そこだけ気をつけてください。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+┈┈┈┈┈┈┈┈┈┈
+👉 顔が赤くなる人は、同じ量でも体への負担が大きい体質です。そこだけ気をつけてください。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -8212,7 +8242,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">毎年、春だけダイエットが止まる人へ。
+      <t xml:space="preserve">🤧 毎年、春だけダイエットが止まる人へ。
 意志の問題じゃないです。
 原因は、鼻にありました。
 花粉症の疲れには</t>
@@ -8287,14 +8317,14 @@
       </rPr>
       <t xml:space="preserve">つがこちらのほうが大きい。鼻が詰まる→口で呼吸する→口の中が乾いて眠りが浅くなる→翌日ずっと眠い。
 つまり鼻を通すことが、疲れの対策になります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 ここで避けられがちなのが、鼻に噴霧するステロイドです。
 「ステロイドは怖い」で使っていない人が多いですが、噴霧タイプは全身に回る量がごく少ないです。そして鼻づまりには、これが効きます。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 さらに、保険で受けられる舌下免疫療法もあります。数年かかりますが、体の反応そのものを変える治療です。
-毎年同じ苦しみを繰り返す前に、一度耳鼻科で相談してみてください。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+👉 毎年同じ苦しみを繰り返す前に、一度耳鼻科で相談してみてください。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -8818,7 +8848,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ダイエットで油を全部抜くと、うまくいかない理由。
+      <t xml:space="preserve">🐟 ダイエットで油を全部抜くと、うまくいかない理由。
 細胞の膜は、食べた脂でできています。
 比喩じゃなく、材料として使われます。
 そしてミトコンドリアにも膜があって、発電の工程はその膜の上に並んでいます。つまり膜の材質が、発電装置の土台です。
@@ -8840,7 +8870,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">が入ると膜がしなやかになり、上に並んだ装置が動きやすくなります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 ここで注意が</t>
     </r>
     <r>
@@ -8896,8 +8926,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">配合」の表示では、どちらなのか区別できません。
-ーーーーー
-やることは週に</t>
+┈┈┈┈┈┈┈┈┈┈
+💡 やることは週に</t>
     </r>
     <r>
       <rPr>
@@ -8985,8 +9015,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年ほど魚を食べていませんでした。理由は面倒だったから。缶詰に変えたら続きました。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -9476,7 +9506,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">コーヒーは、エネルギーを作っていません。
+      <t xml:space="preserve">☕ コーヒーは、エネルギーを作っていません。
 </t>
     </r>
     <r>
@@ -9499,7 +9529,7 @@
 起きているあいだ、体の中に眠気の信号がたまっていきます。カフェインは、その受け取り口に先に入り込んで塞ぎます。
 信号は消えていません。塞がれているだけ。だから抜けると一気に来ます。
 燃料計にテープを貼っても、タンクの中身は変わらないという話です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして半分抜けるまで</t>
     </r>
     <r>
@@ -9554,7 +9584,7 @@
       </rPr>
       <t xml:space="preserve">杯は、寝るときまで残っています。寝つけても深い睡眠は減るので、本人は気づきません。
 私がやったのは、量を減らすことじゃなく時刻を切ることでした。
-・午後</t>
+✅ 午後</t>
     </r>
     <r>
       <rPr>
@@ -9572,7 +9602,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">時以降は水か麦茶
-・朝は起きてすぐより</t>
+✅ 朝は起きてすぐより</t>
     </r>
     <r>
       <rPr>
@@ -9625,10 +9655,10 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">杯だけやめました。それで寝つきが変わりました。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 運動前に使うのは、いい使い方です。睡眠不足を隠すために毎日使うのが、問題でした。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -10152,12 +10182,12 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">サウナは、ダイエットの近道ではないです。
+      <t xml:space="preserve">♨️ サウナは、ダイエットの近道ではないです。
 体への刺激です。
 そして一番効くのは、意外な経路でした。
 熱を受けると、崩れたタンパク質を直す部品が増えます。冷えると、熱を作る組織が活発になります。どちらも適応を引き出します。
 ただ、痩身効果まで期待するのは早いです。人での効果の大きさは、まだ研究が進んでいる段階です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 一番確実に効くのは、睡眠経路でした。
 人は体の中心の温度が下がるときに眠くなります。いったん温めると、そのあと普通より大きく下がる。この下がり方が眠気を呼びます。
 つまり、寝る</t>
@@ -10178,9 +10208,9 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">時間半前が目安です。直前だとまだ熱くて、かえって寝つきが悪くなります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 だから家の風呂で、大部分が取れます。
-・湯船に</t>
+✅ 湯船に</t>
     </r>
     <r>
       <rPr>
@@ -10198,7 +10228,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分
-・最後に足元へぬるいシャワーを</t>
+✅ 最後に足元へぬるいシャワーを</t>
     </r>
     <r>
       <rPr>
@@ -10216,7 +10246,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">秒
-・これを</t>
+✅ これを</t>
     </r>
     <r>
       <rPr>
@@ -10235,9 +10265,9 @@
       </rPr>
       <t xml:space="preserve">回
 水風呂が苦しい私は、これに変えました。睡眠の体感はほぼ同じで、しかも毎日できました。
-飲酒後の入浴だけは、絶対に避けてください。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+⚠️ 飲酒後の入浴だけは、絶対に避けてください。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -10761,11 +10791,11 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">「機能性表示食品」は、国のお墨付きではないです。
+      <t xml:space="preserve">💊 「機能性表示食品」は、国のお墨付きではないです。
 ここは多くの人が誤解しています。
 企業が根拠資料を添えて届け出る制度で、国が中身を審査して許可したものではありません。だます制度ではないですが、トクホとは重さが違います。
-ーーーーー
-見る場所は、裏の</t>
+┈┈┈┈┈┈┈┈┈┈
+💡 見る場所は、裏の</t>
     </r>
     <r>
       <rPr>
@@ -10783,60 +10813,9 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">か所だけです。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、原材料名は「量が多い順」に書かれている
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、「配合」という言葉に量の情報はない
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
+▶︎ 原材料名は「量が多い順」に書かれている
+▶︎ 「配合」という言葉に量の情報はない
+▶︎ </t>
     </r>
     <r>
       <rPr>
@@ -10872,14 +10851,14 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つに入っていなければ、量は少ないということです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 避けたほうがいい売り方も挙げます。
-・病気が治ると書いてある
-・体験談が中心で、成分の説明が薄い
-・解約しにくい定期購入
-・個人輸入のもの
+✅ 病気が治ると書いてある
+✅ 体験談が中心で、成分の説明が薄い
+✅ 解約しにくい定期購入
+✅ 個人輸入のもの
 最後は特に注意です。表示されていない成分が入っていた事例があります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 調べるのは無料です。国立の研究機関が成分ごとの情報を公開しています。薬を飲んでいる方は、薬剤師に成分表示の写真を見せてください。
 買う前の</t>
     </r>
@@ -10899,8 +10878,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">秒で、だいぶ変わります。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -11424,18 +11403,18 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">頑張っているのに痩せない。
+      <t xml:space="preserve">😣 頑張っているのに痩せない。
 このとき、体は非常事態だと思っています。
 コルチゾールは危機対応のホルモンで、短く出て下がるのが正常な形です。でも現代のストレスには終わりがないので、下がるタイミングが来ません。
 そうなると体は、こう判断します。
 「いまは生き延びるときだ」と。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 非常事態が続くと、何が起きるか。
 修理も作り直しも後回しになります。そして、すぐ使える燃料が欲しいので、筋肉を分解しはじめます。
 つまり自分の建物を解体して燃やしている状態です。
 お腹まわりに脂肪がつきやすくなり、糖の処理も落ちます。そして夜にコルチゾールが高いままだと、眠りが浅くなります。
 眠れない→さらに上がる→また眠れない。ぐるぐる回ります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 私はこの時期、食事をさらに減らしました。最悪でした。
 食事制限も体にとっては非常事態です。その上に重ねたので、朝</t>
     </r>
@@ -11474,8 +11453,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分入ることだけです。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -11999,14 +11978,14 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">プロテインを飲んでも変わらないのは、順番が逆だからです。
+      <t xml:space="preserve">🍳 プロテインを飲んでも変わらないのは、順番が逆だからです。
 ミトコンドリアは、ほとんどタンパク質でできています。
 発電の工程を動かす部品も同じです。
 つまりタンパク質は、発電所の建材です。
 でも、材料は使う予定がないと使われません。
 発電所が増えるのは「足りない」と体が判断したときでした。その信号を出すのは運動です。注文が入っていないのに材料だけ届けば、在庫になります。
 これが「飲んでいるのに変わらない」の正体でした。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 量の測り方も、計算をやめたら続きました。
 手のひら</t>
     </r>
@@ -12113,7 +12092,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">日間より、はるかに成果が出ています。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして一番の穴は、朝です。
 トースト。おにぎりだけ。あるいは何も食べない。
 寝ているあいだも材料を使っているので、朝は一番減っている時間帯です。そこに何も入れていない。
@@ -12135,8 +12114,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">個を足すだけで変わります。夜を増やす必要はないです。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -12687,7 +12666,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">朝散歩では、ビタミン</t>
+      <t xml:space="preserve">☀️ 朝散歩では、ビタミン</t>
     </r>
     <r>
       <rPr>
@@ -12725,8 +12704,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つは、別の作業でした。
-・朝の光は、目から入れて体内時計を合わせる
-・ビタミン</t>
+✅ 朝の光は、目から入れて体内時計を合わせる
+✅ ビタミン</t>
     </r>
     <r>
       <rPr>
@@ -12745,7 +12724,7 @@
       </rPr>
       <t xml:space="preserve">は、昼に皮膚を出して作る
 時間帯も使う場所も違います。両方やる必要があります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 日本では足りていない人がかなり多いです。
 理由は</t>
     </r>
@@ -12765,9 +12744,9 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つ。室内中心の生活、日焼け対策、多く含む食品が少ないこと、そして冬は太陽の角度のせいで作れないこと。
-ーーーーー
-やることは簡単です。
-・午前</t>
+┈┈┈┈┈┈┈┈┈┈
+💡 やることは簡単です。
+✅ 午前</t>
     </r>
     <r>
       <rPr>
@@ -12802,7 +12781,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">時のあいだに外へ
-・夏なら</t>
+✅ 夏なら</t>
     </r>
     <r>
       <rPr>
@@ -12837,8 +12816,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分、腕か脚を出す
-・顔は日焼け止めのままでいい
-・冬は割り切って、魚で補う
+✅ 顔は日焼け止めのままでいい
+✅ 冬は割り切って、魚で補う
 日焼けするまで当たる必要はないです。赤くなっても、ビタミン</t>
     </r>
     <r>
@@ -12858,10 +12837,10 @@
       </rPr>
       <t xml:space="preserve">は増えません。
 太陽を直視しないことだけ、守ってください。
-ーーーーー
-高用量のサプリは、摂りすぎが起こります。日光では過剰になりませんが、サプリは別です。そこだけ注意してください。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+┈┈┈┈┈┈┈┈┈┈
+⚠️ 高用量のサプリは、摂りすぎが起こります。日光では過剰になりませんが、サプリは別です。そこだけ注意してください。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -13385,11 +13364,11 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">運動も睡眠も整えたのに、まだだるい。
+      <t xml:space="preserve">🥜 運動も睡眠も整えたのに、まだだるい。
 最後の鍵が抜けているかもしれません。
 ミトコンドリアが作るエネルギーは、単体では働きません。マグネシウムと組んだ状態で、はじめて使える形になります。
 つまり発電はできているのに、取り出せないままになっている。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして厄介なのが、ここは血液検査で分からないことです。
 体内のマグネシウムは、ほとんどが骨と細胞の中にあります。血液にあるのはごく一部で、足りなくなると骨から引き出して濃さを保ちます。
 だから蓄えが空でも、数値は正常に出ます。
@@ -13411,13 +13390,13 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">は「検査が先」でしたが、ここは食事から足して様子を見ていい場所です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 疑っていいサインを挙げます。
-・足がよくつる
-・まぶたがピクピクする
-・便が固い
-・寝つきが悪い
-・いつも肩が張っている
+✅ 足がよくつる
+✅ まぶたがピクピクする
+✅ 便が固い
+✅ 寝つきが悪い
+✅ いつも肩が張っている
 </t>
     </r>
     <r>
@@ -13453,7 +13432,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つ重なるなら、試す価値があります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 私がやったのは</t>
     </r>
     <r>
@@ -13507,9 +13486,9 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">週間で夜中の足のつりが止まりました。
-腎臓に病気がある方は、ここだけは自己判断で続けないでください。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+⚠️ 腎臓に病気がある方は、ここだけは自己判断で続けないでください。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -14033,18 +14012,18 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">「代謝が落ちた」の正体は、年齢じゃないです。
+      <t xml:space="preserve">⚡ 「代謝が落ちた」の正体は、年齢じゃないです。
 細胞の中の発電所が、数と働きを落としています。
 その発電所がミトコンドリアです。
 ここで知っておくと得をすることがあります。
 痩せることと、きれいになることと、疲れないことは、同じ電力を使っています。
 肌の細胞を作り替えるのも、傷んだ場所を修理するのも、食べたものを燃やすのも、全部同じエネルギーです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 だから別々の対策は必要ないんです。
 発電量が落ちれば全部まとめて落ちるし、戻れば全部まとめて戻ります。
 そして発電所は増やせます。生まれつきで決まっているわけではないです。
-ーーーーー
-やることは地味な</t>
+┈┈┈┈┈┈┈┈┈┈
+💡 やることは地味な</t>
     </r>
     <r>
       <rPr>
@@ -14062,7 +14041,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つだけ。
-・少しきつい有酸素を週</t>
+✅ 少しきつい有酸素を週</t>
     </r>
     <r>
       <rPr>
@@ -14097,7 +14076,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分
-・筋トレを週</t>
+✅ 筋トレを週</t>
     </r>
     <r>
       <rPr>
@@ -14115,7 +14094,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">回
-・睡眠</t>
+✅ 睡眠</t>
     </r>
     <r>
       <rPr>
@@ -14133,7 +14112,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">時間を死守
-・タンパク質と鉄とビタミン</t>
+✅ タンパク質と鉄とビタミン</t>
     </r>
     <r>
       <rPr>
@@ -14152,7 +14131,7 @@
       </rPr>
       <t xml:space="preserve">群
 「会話はできるけど歌うのはつらい」強さが目安です。楽な運動では、足りないと判断されません。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして</t>
     </r>
     <r>
@@ -14206,7 +14185,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つずつ積んだ人は半年後も続けています。
-まず睡眠だけ</t>
+👉 まず睡眠だけ</t>
     </r>
     <r>
       <rPr>
@@ -14224,8 +14203,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">週間。それが当たり前になってから次を足してください。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -14749,7 +14728,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">「とりあえず水を飲め」で終わる話に、ずっと納得できませんでした。
+      <t xml:space="preserve">💧 「とりあえず水を飲め」で終わる話に、ずっと納得できませんでした。
 理由を言わずに量だけ指定されるからです。
 水の役割は</t>
     </r>
@@ -14771,7 +14750,7 @@
       <t xml:space="preserve">つ。運ぶことです。
 酸素と栄養を細胞まで届け、老廃物を腎臓まで運び、熱を回して体温を保つ。要するに物流です。
 つまり、どんないい材料を入れても運べなければ届きません。倉庫の外に積まれたままになります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして「</t>
     </r>
     <r>
@@ -14861,7 +14840,7 @@
       </rPr>
       <t xml:space="preserve">杯足す。
 道具もお金もいらない指標です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 飲み方のコツを</t>
     </r>
     <r>
@@ -14880,7 +14859,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つ。
-・起きてすぐ</t>
+✅ 起きてすぐ</t>
     </r>
     <r>
       <rPr>
@@ -14898,7 +14877,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">杯
-・食事の前に</t>
+✅ 食事の前に</t>
     </r>
     <r>
       <rPr>
@@ -14916,7 +14895,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">杯
-・</t>
+✅ </t>
     </r>
     <r>
       <rPr>
@@ -15003,11 +14982,11 @@
       </rPr>
       <t xml:space="preserve">回に分ける
 一度にたくさん飲んでも、体はためておけません。こまめに入れるほうが効率がいいです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 ただし一気飲みはしないでください。
-短時間に大量だと、血液の塩分が薄まりすぎて危険です。心臓や腎臓の治療中の方は、主治医の指示が優先です。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+⚠️ 短時間に大量だと、血液の塩分が薄まりすぎて危険です。心臓や腎臓の治療中の方は、主治医の指示が優先です。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -15558,7 +15537,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">昨日から</t>
+      <t xml:space="preserve">⚖️ 昨日から</t>
     </r>
     <r>
       <rPr>
@@ -15615,11 +15594,11 @@
       </rPr>
       <t xml:space="preserve">キロも、ほとんど水です。
 体重計が測っているのは総重量で、脂肪ではないんです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 体組成計の数字も、正直に書きます。
 体に弱い電気を流して推定しているので、体の水の量で大きく変わります。朝と夜で違い、水を飲んだ直後でも違う。
 絶対値の精度は高くないです。「体内年齢」などは各社が独自に計算しているものです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 私は毎日</t>
     </r>
     <r>
@@ -15726,9 +15705,9 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">センチ減っていました。
-体重だけ見ていたら、やめていたはずです。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+⚠️ 体重だけ見ていたら、やめていたはずです。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -16252,7 +16231,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">危ないのは真夏より、最初の暑い日です。
+      <t xml:space="preserve">🌡️ 危ないのは真夏より、最初の暑い日です。
 体が暑さに慣れるには</t>
     </r>
     <r>
@@ -16307,16 +16286,16 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月の急に暑くなった日が、一番対応能力が低い。だから対策は体感を待たず、暦で先回りします。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして夏に起きることで、あまり語られないものがあります。
 筋肉が落ちます。
 食欲が落ちて、そうめんや冷やし中華が中心になる。炭水化物の単独食いです。運動量も減ります。
 建材が入らず刺激も減れば、筋肉は落ちます。夏に体重が落ちて喜ぶ人がいますが、中身が筋肉なら秋に戻りにくい体になっています。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 冷たいままタンパク質を足してください。
-・冷やし中華に卵とハムと鶏肉
-・そうめんに納豆やツナ
-・冷や奴を</t>
+✅ 冷やし中華に卵とハムと鶏肉
+✅ そうめんに納豆やツナ
+✅ 冷や奴を</t>
     </r>
     <r>
       <rPr>
@@ -16335,7 +16314,7 @@
       </rPr>
       <t xml:space="preserve">品
 熱いものを食べる必要はないです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 命に関わる話も</t>
     </r>
     <r>
@@ -16356,8 +16335,8 @@
       <t xml:space="preserve">つ。
 夜もエアコンを使ってください。室内での夜間熱中症が起きています。高齢の方は暑さを感じにくいので、体感ではなく室温で判断を。
 冬は入浴の手順です。脱衣所を暖めて、湯温を上げすぎず、飲酒後は入らないこと。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -16881,7 +16860,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">手足が冷たいのを「体質だから」で諦めていませんか。
+      <t xml:space="preserve">🧦 手足が冷たいのを「体質だから」で諦めていませんか。
 冷えは原因ではなく、結果です。
 熱はわざわざ作っているものではなく、発電の副産物です。パソコンが温かくなるのと同じで、変換が</t>
     </r>
@@ -16902,7 +16881,7 @@
       </rPr>
       <t xml:space="preserve">パーセントではないから出てくる。
 つまり冷えは、発電量が足りていないという報告です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 ここから、言いにくい話をします。
 ダイエットで寒くなったなら、それは失敗のサインです。
 私は昔、食事を半分に落として</t>
@@ -16959,7 +16938,7 @@
       </rPr>
       <t xml:space="preserve">か月で全部戻りました。
 体重が落ちていても、やり方を変えるべき状態でした。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして温めるなら、手足より先に中心です。
 中心が冷えると、体は熱を逃がさないために末端への血流を絞ります。だから手足の冷たさは結果なんです。
 靴下</t>
@@ -16997,12 +16976,12 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">枚のほうが効きます。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 冷えは体重より早く動く指標です。
 体重は数週間かかりますが、手先の温度は数日で変わりはじめます。だからこれを見ながら進めるほうが効率的です。
-急な寒がりと疲れが重なるなら、甲状腺と鉄も調べてください。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+👉 急な寒がりと疲れが重なるなら、甲状腺と鉄も調べてください。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -17526,18 +17505,18 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">「深呼吸して酸素をたくさん取り込みましょう」
+      <t xml:space="preserve">💨 「深呼吸して酸素をたくさん取り込みましょう」
 これ、半分間違いです。
 健康な人の血液は、すでに酸素でほぼ満タンです。だから深く吸っても、積み込める量はほとんど増えません。
 知ったときはがっかりしました。深呼吸は意味がないのか、と。
 でも調べると、変えているものが別にありました。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 酸素を現場で降ろす作業です。
 ここで鍵になるのが二酸化炭素です。廃棄物だと思われていますが、十分にあると血液は酸素を離しやすくなります。つまり降ろす合図になっています。
 だから速く浅い呼吸を続けると、吐きすぎて合図が弱くなります。酸素を持っているのに、現場で渡さない。
 これが、呼吸が速い人が苦しくなる理由のひとつです。
-ーーーーー
-やることは</t>
+┈┈┈┈┈┈┈┈┈┈
+💡 やることは</t>
     </r>
     <r>
       <rPr>
@@ -17609,7 +17588,7 @@
       </rPr>
       <t xml:space="preserve">分だけ。
 無理に深く吸わなくていいです。むしろ吸いすぎないほうがいい。ゆっくり吐くことだけ意識してください。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 私は</t>
     </r>
     <r>
@@ -17663,8 +17642,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">週間で夕方の頭の重さが減りました。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -18188,15 +18167,15 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">在宅勤務になってから、体が重い。
+      <t xml:space="preserve">🏠 在宅勤務になってから、体が重い。
 通勤がなくなって楽になったのに、なぜか疲れが抜けない。
 理由は単純でした。通勤が運動だったんです。
 駅まで歩く。階段を上る。乗り換えで歩く。会社の中を移動する。昼食に出る。全部なくなりました。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして奪われたのは、動きだけじゃなかった。
 外に出ないので朝の光を浴びなくなり、体内時計がずれます。帰りの電車がなくなったので、仕事と休みの境目も消えました。
 どれも努力していたものではないので、失ったことに気づけません。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 一番効いたのは「偽の通勤」でした。
 仕事の前と後に、外を</t>
     </r>
@@ -18234,12 +18213,12 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つ同時に取れます。朝の光、歩く量、そして仕事の切り替え。歩いて帰ってくると、終わった感覚が出ます。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 机は数千円で整います。
-・本を積んで画面を目の高さに
-・キーボードは別に用意
-・足の裏を床につける
-・</t>
+✅ 本を積んで画面を目の高さに
+✅ キーボードは別に用意
+✅ 足の裏を床につける
+✅ </t>
     </r>
     <r>
       <rPr>
@@ -18258,7 +18237,7 @@
       </rPr>
       <t xml:space="preserve">分でタイマー
 高い椅子より、まずここです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 あとは冷蔵庫。</t>
     </r>
     <r>
@@ -18278,8 +18257,8 @@
       </rPr>
       <t xml:space="preserve">歩で開けられるのが問題でした。お菓子を買うのをやめて、ゆで卵とナッツを手前に置いただけです。
 我慢ではなく、置くものを変える。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -18830,7 +18809,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">正しい姿勢を</t>
+      <t xml:space="preserve">🪑 正しい姿勢を</t>
     </r>
     <r>
       <rPr>
@@ -18885,7 +18864,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つの形で固まるようにできていないんです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして、ここは正直に書きます。
 姿勢の形と痛みの関係は、思われているほど強くないです。研究でもかなり揺れている部分です。
 猫背の人が全員痛めるわけでも、きれいな姿勢の人が無縁なわけでもない。
@@ -18925,7 +18904,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分ごとに形を変えるのとでは、はっきり差が出ます。つまり一番いい姿勢は、次の姿勢です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 私がやったのは、ストレッチではなく環境のほうでした。
 ノートパソコンをそのまま机に置いて、ずっと下を向いていた。頭は重いので、首と肩が常に働いている状態です。
 本を積んで画面を目の高さまで上げ、キーボードを別にしました。</t>
@@ -18947,10 +18926,10 @@
       </rPr>
       <t xml:space="preserve">週間で夕方の首の固さが減りました。
 ほぐすより、ほぐす必要がない状態にするほうが早かったです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 矯正ベルトは、長く頼ると自分の筋肉が使われなくなります。短期で痛みをしのぐ以外は、慎重に。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -19474,21 +19453,21 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">家族に体にいいことを教えて、嫌な顔をされたことはないですか。
+      <t xml:space="preserve">🏡 家族に体にいいことを教えて、嫌な顔をされたことはないですか。
 私は何度もやって、何度も失敗しました。
 言われたのはこれです。
 「また始まった」「わかってるから言わないで」
 当時は理解できませんでした。よくなることを伝えているのに、なぜ嫌がるのか。
 いま分かります。正しさを持ち出すと、相手は責められた側になるんです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 だから、人ではなく環境を変えます。
 家族は同じ冷蔵庫、同じ食卓、同じ買い物の結果を使っています。だから環境を変えれば、黙っていても広がります。
 しかも、相手の同意はいりません。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 一番効くのは買い物の中身でした。
 家にないものは食べられない。つまり選択は、買い物の時点で終わっています。
 そして引くのではなく、足します。
-・ゆで卵を</t>
+✅ ゆで卵を</t>
     </r>
     <r>
       <rPr>
@@ -19506,11 +19485,11 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">個作って手前に置く
-・ナッツを小皿に出す
-・さば缶を箱で買う
-・味噌汁にわかめときのこ
+✅ ナッツを小皿に出す
+✅ さば缶を箱で買う
+✅ 味噌汁にわかめときのこ
 説明は一切しません。置くだけです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 誘うときは「散歩行くけど、来る</t>
     </r>
     <r>
@@ -19547,9 +19526,9 @@
       </rPr>
       <t xml:space="preserve">人で行きます。
 半年後、家族が自分からさば缶を食べるようになりました。一度も説明していません。
-子どもには、体型のことを言わないでください。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+👉 子どもには、体型のことを言わないでください。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -20073,16 +20052,16 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">先に、一番大事なことを書きます。
+      <t xml:space="preserve">🏥 先に、一番大事なことを書きます。
 この話を読んで、薬を自己判断でやめないでください。
 血圧、血糖、心臓、血を固まりにくくする薬。勝手にやめると命に関わります。やめたときのリスクのほうが、ほとんどの場合で大きいです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そのうえで、抜け落ちやすい話をします。
 薬は医師が管理します。食事は自分で決めます。その間に、誰も見ていない隙間ができます。
 いくつかの薬は、特定の栄養素を減らすことが分かっています。隠されているわけではなく、患者側に伝わっていないだけです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 知られている組み合わせを挙げます。
-・胃酸を抑える薬 → ビタミン</t>
+✅ 胃酸を抑える薬 → ビタミン</t>
     </r>
     <r>
       <rPr>
@@ -20100,7 +20079,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">、鉄、マグネシウム
-・糖尿病のメトホルミン → ビタミン</t>
+✅ 糖尿病のメトホルミン → ビタミン</t>
     </r>
     <r>
       <rPr>
@@ -20110,16 +20089,16 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">B12
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・尿を増やす薬 → カリウム、マグネシウム
-・ステロイド → 骨と筋肉
+✅ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">尿を増やす薬 → カリウム、マグネシウム
+✅ ステロイド → 骨と筋肉
 コレステロールの薬は、コエンザイム</t>
     </r>
     <r>
@@ -20138,14 +20117,14 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">を減らします。これはミトコンドリアで電子を運ぶ部品です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 サプリ側の注意も。
 ワルファリンを飲んでいる方は納豆と青汁を避けます。セントジョーンズワートは多くの薬の効き方を変えます。
-ーーーーー
-やることは、次の受診で一言聞くだけです。
+┈┈┈┈┈┈┈┈┈┈
+💡 やることは、次の受診で一言聞くだけです。
 「この薬で、不足しやすくなる栄養素はありますか」
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -20696,7 +20675,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">体質改善について</t>
+      <t xml:space="preserve">🗺️ 体質改善について</t>
     </r>
     <r>
       <rPr>
@@ -20751,7 +20730,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つ。しかも全部無料です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 体を発電所の集まりと見ると、情報が</t>
     </r>
     <r>
@@ -20771,7 +20750,7 @@
       </rPr>
       <t xml:space="preserve">枚の地図になります。
 痩せることと、きれいになることと、疲れないことは、同じ電力を使っているからです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして順番の一番上は「足すこと」ではないです。
 削っているものを止めるほうが先。穴の空いたバケツに水を入れても、たまりません。
 桁違いに大きい穴は</t>
@@ -20792,7 +20771,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つ。たばこと、お酒の量です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 土台は</t>
     </r>
     <r>
@@ -20811,8 +20790,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つで、全部無料です。
-・起きたらカーテンを開ける
-・睡眠</t>
+✅ 起きたらカーテンを開ける
+✅ 睡眠</t>
     </r>
     <r>
       <rPr>
@@ -20830,7 +20809,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">時間を下回らない
-・</t>
+✅ </t>
     </r>
     <r>
       <rPr>
@@ -20848,7 +20827,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分ごとに立つ
-・夜</t>
+✅ 夜</t>
     </r>
     <r>
       <rPr>
@@ -20866,7 +20845,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">時までに食べ終える
-・靴のサイズを測ってもらう
+✅ 靴のサイズを測ってもらう
 多くの人は、ここで変わります。買うものが</t>
     </r>
     <r>
@@ -20885,7 +20864,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つもない部分だからです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 材料を足すのは、土台が整ってから。
 そして自分では見えないものが</t>
     </r>
@@ -20940,8 +20919,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年、逆の順番でやっていました。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -21466,7 +21445,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">⏱️ 1</t>
     </r>
     <r>
       <rPr>
@@ -21511,7 +21490,7 @@
       <t xml:space="preserve">時間座っていたら相殺されません。
 これ、知らずに頑張っている人が本当に多いです。
 運動と座りすぎは、別々に効いてきます。運動はプラスを作り、座りすぎはマイナスを作る。プラスを足してもマイナスは消えず、両方が残ります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 座っているあいだ、何が起きているか。
 筋肉は動いた瞬間に、血液から糖を取り込みます。動かなければ処理が始まりません。
 血液の中の脂肪を片づける働きも、使わないと数時間で落ちます。
@@ -21567,12 +21546,12 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">時間は止まったままです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そしてふくらはぎは第二の心臓です。
 縮むと血管が押されて、血液が上に押し上げられます。座ると、このポンプが止まります。
 だから足がむくみ、足先が冷えます。夕方に靴が窮屈になるのは、これが理由です。
-ーーーーー
-対策は</t>
+┈┈┈┈┈┈┈┈┈┈
+💡 対策は</t>
     </r>
     <r>
       <rPr>
@@ -21607,8 +21586,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分。内容は決めません。
-・立つだけ
-・かかと上げ</t>
+✅ 立つだけ
+✅ かかと上げ</t>
     </r>
     <r>
       <rPr>
@@ -21626,7 +21605,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">回
-・部屋を</t>
+✅ 部屋を</t>
     </r>
     <r>
       <rPr>
@@ -21644,7 +21623,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">周
-・階段を</t>
+✅ 階段を</t>
     </r>
     <r>
       <rPr>
@@ -21697,8 +21676,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">週間でむくみが減りました。筋トレを増やしたときより体感が早かったです。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -22266,7 +22245,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">「</t>
+      <t xml:space="preserve">⏰ 「</t>
     </r>
     <r>
       <rPr>
@@ -22304,15 +22283,15 @@
 気になって調べて、少しがっかりしました。
 この手の数字の多くは動物実験から来ています。人で同じ時間に同じことが起きる保証はないんです。
 オートファジーという働き自体は実在します。でも「何時間でどのくらい進むか」は、人ではまだはっきりしていません。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 試験の結果も正直に書きます。
 時間を絞ると体重は落ちます。ただし「同じカロリーを普通に食べた場合」と大きく変わらないことが多い。
 つまり、時間を絞って食べる量が減っている部分がかなりあります。時間そのものに魔法があるわけではないです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 では意味がないのか。そうでもないです。
 食事は内臓の時計を動かすスイッチです。夜遅くに食べると、内臓は「まだ昼だ」と判断します。
 脳は夜、内臓は昼。このズレが起きると、整備の作業が噛み合いません。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 私は</t>
     </r>
     <r>
@@ -22385,8 +22364,8 @@
       </rPr>
       <t xml:space="preserve">時間です。
 こっちのほうが結果が出ました。長さより、位置でした。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -22911,7 +22890,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t xml:space="preserve">✈️ 3</t>
     </r>
     <r>
       <rPr>
@@ -22958,7 +22937,7 @@
 でも旅行では、同時に起きます。
 起きる時刻がずれる。寝る時間が減る。長時間座る。食事の時刻がずれる。外食で内容が変わる。お酒が増える。水が足りなくなる。
 土台が全部です。だから帰ったあとの疲れが大きい。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 ここで完璧を目指すと、全部やめることになります。
 だから守るのは</t>
     </r>
@@ -22978,8 +22957,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つだけにしました。
-・起きる時刻を、家と同じにする
-・</t>
+✅ 起きる時刻を、家と同じにする
+✅ </t>
     </r>
     <r>
       <rPr>
@@ -22999,7 +22978,7 @@
       <t xml:space="preserve">食にタンパク質をひとつ足す
 寝る時刻は守れません。会食も移動も自分で決められないからです。でも起きる時刻は、わりと守れます。そして体内時計は、起きる時刻で決まります。
 運動はしなくていいです。欲張ると全部できなくなります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 私は朝一番の便をやめました。</t>
     </r>
     <r>
@@ -23053,12 +23032,12 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">時になり、それだけで帰宅後の重さが減りました。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 帰ってから取り返そうとしないでください。
 食事を減らすのは逆効果です。いつもの時刻に起きて光を浴びる。それで戻りはじめます。
 薬を飲んでいる方は、時差での服用時刻を出発前に薬剤師へ。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -23582,7 +23561,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">「年齢的にそういう時期だから」
+      <t xml:space="preserve">🌸 「年齢的にそういう時期だから」
 この言い方が、一番よくないと思っています。
 考えるのをやめさせる言葉だからです。
 更年期に起きることには、仕組みがあります。
@@ -23604,7 +23583,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つ減ると、連鎖します。筋肉が落ちやすくなる。脂肪がお腹まわりに移る。糖の処理が落ちる。そして睡眠が崩れて、全部が増幅されます。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 ここで一番伝えたいことがあります。
 代謝が落ちる主因は、年齢そのものではないです。
 内訳は「筋肉が減った分」「動く量が減った分」「純粋な加齢の分」で、最後は思われているより小さい。そして前の</t>
@@ -23627,14 +23606,14 @@
       <t xml:space="preserve">つは変えられます。
 つまりこの時期こそ、筋トレとタンパク質の価値が上がります。
 「年齢だから運動はやめておこう」が、一番まずい判断です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして、知らないまま我慢する必要はないです。
 症状がつらいなら婦人科で相談できます。ホルモンを補う治療も選択肢として存在します。始める時期や既往で判断が変わるので、自分の場合どうなのかを聞いてください。
 甲状腺の病気も症状が似ているので、検査で切り分けられます。
 保険で聞けることを聞いていないのが、一番もったいないです。
-閉経後の出血は、量が少なくても必ず受診してください。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+⚠️ 閉経後の出血は、量が少なくても必ず受診してください。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -24141,12 +24120,12 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">夜、布団に入っても眠くならない。
+      <t xml:space="preserve">🌅 夜、布団に入っても眠くならない。
 スマホをやめても目が冴えている。
 それで「寝る前の行動が悪いんだろう」と考えますよね。
 でも、そこだけ直しても足りないです。
 原因は朝にありました。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 体内時計は少しずつ後ろにずれるので、毎朝セットし直す必要があります。そのセットに使われるのが光です。
 そして時計が合うと、タイマーが動き出します。眠気を作るホルモンが出る時刻が、そこで決まる。
 朝に光を浴びてから、だいたい</t>
@@ -24185,7 +24164,7 @@
       </rPr>
       <t xml:space="preserve">時間後です。
 つまり夜の眠気は、その日の朝に予約されています。朝にスタートを切っていなければ、夜の眠気も遅れます。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 もう</t>
     </r>
     <r>
@@ -24207,8 +24186,8 @@
 室内の明るさでは足りません。
 人の目は明るさの違いに鈍いので気づきませんが、曇りの日の屋外でも室内よりはるかに強いです。
 「今日は曇りだから意味がない」はもったいないです。
-ーーーーー
-やることはカーテンを開けるだけ。
+┈┈┈┈┈┈┈┈┈┈
+💡 やることはカーテンを開けるだけ。
 起きて</t>
     </r>
     <r>
@@ -24262,9 +24241,9 @@
       </rPr>
       <t xml:space="preserve">分。できればガラス越しではなく外に出てください。ゴミ出しのついででいいです。
 私は遮光カーテンで真っ暗にして寝て、暗い部屋で起きていました。開けただけで、数日で寝つきが変わりました。
-太陽を直視しないことだけ、守ってください。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+👉 太陽を直視しないことだけ、守ってください。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -24788,7 +24767,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">歩こうと決めて、</t>
+      <t xml:space="preserve">👟 歩こうと決めて、</t>
     </r>
     <r>
       <rPr>
@@ -24827,15 +24806,15 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つだけ設備が必要で、それが靴でした。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして靴選びで一番効くのは、機能ではなかったです。
 足の形から最適な靴を決める考え方は、根拠が強くないんです。アーチを矯正する靴がけがを防ぐ効果は、研究で確認されていません。
 効くのは「履いて快適かどうか」でした。ここは比較的しっかりした裏付けがあります。
 つまり理屈より、感覚です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 あとはサイズです。多くの人は小さく、幅の狭い靴を履いています。
-・夕方に測る（足は夕方のほうが大きい）
-・つま先に</t>
+✅ 夕方に測る（足は夕方のほうが大きい）
+✅ つま先に</t>
     </r>
     <r>
       <rPr>
@@ -24853,8 +24832,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">センチの余裕
-・幅がきつくない
-・かかとが浮かない
+✅ 幅がきつくない
+✅ かかとが浮かない
 私は</t>
     </r>
     <r>
@@ -24943,8 +24922,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分です。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -25468,14 +25447,14 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">歯の話は、体質改善と関係ない。
+      <t xml:space="preserve">🦷 歯の話は、体質改善と関係ない。
 私もそう思っていました。
 でも、かなり強くつながっています。
 歯ぐきの病気は炎症です。そして炎症はエネルギーを使います。免疫の働きには電力が必要だからです。
 問題は、これが終わらないことです。
 風邪の炎症は数日で終わる。けがも治れば終わる。でも歯ぐきの炎症は何年も続きます。
 つまり、消えない小さな火事が口の中にある。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 もう</t>
     </r>
     <r>
@@ -25496,7 +25475,7 @@
       <t xml:space="preserve">つ。口は腸より前にある入口です。
 噛めなくなると、硬いものを避けます。肉より柔らかいもの、生野菜より煮たもの。つまりタンパク質と食物繊維が同時に減ります。
 食事に気をつけているつもりでも、噛めないものは選べません。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 私は毎日</t>
     </r>
     <r>
@@ -25569,9 +25548,9 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">週間で出なくなりました。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 虫歯は量より回数が効きます。だらだら食べをやめてください。
-</t>
+⚠️ </t>
     </r>
     <r>
       <rPr>
@@ -25589,8 +25568,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">週間以上治らない口の中の傷は、必ず受診を。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -26114,23 +26093,23 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">添加物は危険。水道水は飲むな。調理器具を変えろ。
+      <t xml:space="preserve">🧪 添加物は危険。水道水は飲むな。調理器具を変えろ。
 この手の話に、長く振り回されました。
 調べるほど怖いものが増えて、何も食べられなくなっていく。
 でも、あるとき気づきました。怖がる順番が逆だったんです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 影響の大きさには、桁の違いがあります。
 桁違いに大きいのは、たばことお酒の量。
 次に睡眠不足と運動不足と座位時間。
 その次に加工肉。
 個別の添加物や調理器具は、ずっと下です。
 たばこを吸いながら添加物を気にするのは、家が燃えているときに台所の洗剤を気にしている状態です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 添加物についても正直に書きます。
 通常の食べ方で、個別の添加物に起因する害の根拠は強くないです。
 一方で加工肉には、控える根拠があります。そして個別の成分より「加工度」のほうが効いている可能性が高い。
 無添加のお菓子は、お菓子です。添加物がなくても繊維もタンパク質もない。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 私は表示のカタカナを数えるのをやめました。
 かわりにタンパク質と繊維を見るようにしたら、買い物が</t>
     </r>
@@ -26150,7 +26129,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分で終わるようになりました。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 無料でできる現実的な対策は</t>
     </r>
     <r>
@@ -26169,13 +26148,13 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つ。
-・プラスチック容器のまま加熱しない
-・調理中は換気する
-・真っ黒な焦げは食べない
-・フライパンを空焼きしない
-中毒の診断がないキレーションは危険です。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+✅ プラスチック容器のまま加熱しない
+✅ 調理中は換気する
+✅ 真っ黒な焦げは食べない
+✅ フライパンを空焼きしない
+⚠️ 中毒の診断がないキレーションは危険です。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -26699,17 +26678,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">寝不足の翌日、やたら甘いものが欲しくなる。
+      <t xml:space="preserve">😴 寝不足の翌日、やたら甘いものが欲しくなる。
 そして「意志が弱いな」と自分を責める。
 それ、違います。体がそう要求しているんです。
 寝不足になると食欲を強める側のホルモンが増え、満腹を伝える側が減ります。アクセルが踏まれてブレーキが外れた状態。
 この状態で我慢する勝負は、だいたい負けます。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして寝ているあいだに何が起きているか。
 ミトコンドリアは使うと傷みます。発電の副産物でサビが出て、発電所自体を傷つけるからです。
 その傷んだ分を回収して、新しいものに入れ替える作業が、休んでいるあいだに進みます。工場を動かしながら同じ設備を分解するのは無理ですよね。
 つまり睡眠は、整備のために確保された時間です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 寝不足の</t>
     </r>
     <r>
@@ -26745,9 +26724,9 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つ。
-・食欲のアクセルが踏まれる
-・糖の処理能力が落ちる
-・運動の強度が出ない
+✅ 食欲のアクセルが踏まれる
+✅ 糖の処理能力が落ちる
+✅ 運動の強度が出ない
 </t>
     </r>
     <r>
@@ -26766,7 +26745,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">方向から同時に効くので、食事だけで取り返すのはしんどいです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして長さより先に見るべきは、時刻でした。
 深い睡眠は夜の前半に集中します。だから同じ</t>
     </r>
@@ -26856,8 +26835,8 @@
       <t xml:space="preserve">時間は別物です。
 起きる時刻をそろえるほうが、増やすより簡単です。
 いびきを指摘されるなら、習慣では解決しません。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -27381,7 +27360,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">吸っている方には読みづらい話だと思います。
+      <t xml:space="preserve">🚭 吸っている方には読みづらい話だと思います。
 責めるつもりはないです。仕組みだけ書きます。
 体質改善の対策を</t>
     </r>
@@ -27419,7 +27398,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">か所同時に効くからです。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 </t>
     </r>
     <r>
@@ -27475,11 +27454,11 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つ目。有害物質が発電所自体を傷つけ、サビを増やします。整備が追いつかなくなります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして「吸うと落ち着く」の正体も書いておきます。
 あれはニコチンが切れた不快が消えているだけで、ゼロに戻っています。プラスにはなっていない。
 吸わない人は、その不快をそもそも感じていません。だからやめて数週間の人は「イライラが減った」と言います。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 最初の変化は</t>
     </r>
     <r>
@@ -27517,8 +27496,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">人でやる必要はないです。保険で相談できる窓口があります。まず条件を聞くだけでいいです。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -28042,19 +28021,19 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">体にいいものを選んでいる。タンパク質も意識している。サプリも飲んでいる。
+      <t xml:space="preserve">🦠 体にいいものを選んでいる。タンパク質も意識している。サプリも飲んでいる。
 なのに変わらない。
 こういうとき、見る場所は決まっています。入口です。
 どれだけいいものを食べても、取り込めなければ届きません。荷物が玄関に置かれたままの状態です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして、ここが面白いところでした。
 腸内細菌のエサは食物繊維です。人は繊維を分解できませんが、細菌はできます。そして分解した結果、別の物質を作り出します。
 その物質が、大腸の細胞のエネルギー源になります。
 つまり腸の細胞は、あなたが直接食べたものではなく、細菌が作ったものを主な燃料にしている。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 だから繊維が足りないと、入口を管理している細胞が燃料不足になります。
 壁の管理が緩み、免疫が働き、電力が火消しに回ります。修理や肌の作り替えに回る分が減ります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 私は繊維をいきなり山盛り増やして失敗しました。
 お腹が張って、ガスもすごい。体調は前より悪くなった。そこで「合わない」と結論を出してやめました。
 原因は</t>
@@ -28145,8 +28124,8 @@
       </rPr>
       <t xml:space="preserve">週間かけたら、張りませんでした。
 菌のサプリより、エサが先です。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -28670,7 +28649,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">昼ごはんのあと、強烈に眠くなる。午後</t>
+      <t xml:space="preserve">📉 昼ごはんのあと、強烈に眠くなる。午後</t>
     </r>
     <r>
       <rPr>
@@ -28693,11 +28672,11 @@
 上がり方と、下がり方の問題でした。
 急に上がると、体は急に下げようとします。そして下がりすぎる。この下がった瞬間に、強い眠気と空腹が来ます。
 午後の眠気と夕方の間食は、ほぼこれが原因です。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 発電所には処理の速さに上限があります。
 一気に燃料が来ても速く燃やせないので、余った分は蓄えに回ります。つまり同じ量でも、一気に来ると余る分が増えます。
-ーーーーー
-対策は我慢じゃないです。
+┈┈┈┈┈┈┈┈┈┈
+💡 対策は我慢じゃないです。
 野菜やタンパク質を先に、ごはんを後に。これだけで上がり方がゆるやかになります。
 一番やってはいけないのは、おにぎりだけ、うどんだけの単独食いです。糖だけが単独で入ってくるので、遅らせるものが何もない。
 コンビニでも、ゆで卵</t>
@@ -28718,7 +28697,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">個かサラダを足すだけで変わります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 もう</t>
     </r>
     <r>
@@ -28791,8 +28770,8 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">週間で午後の眠気が減りました。内容は何も変えていません。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -29316,7 +29295,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">有酸素がいいのか、筋トレがいいのか、</t>
+      <t xml:space="preserve">🏃 有酸素がいいのか、筋トレがいいのか、</t>
     </r>
     <r>
       <rPr>
@@ -29353,9 +29332,9 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">つは別の仕事をしています。ドライバーとハンマーのどちらが優れているか、という議論に似ています。
-ーーーーー
-・有酸素は、発電所の数を増やす
-・</t>
+┈┈┈┈┈┈┈┈┈┈
+✅ 有酸素は、発電所の数を増やす
+✅ </t>
     </r>
     <r>
       <rPr>
@@ -29373,10 +29352,10 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">は、短時間で同じ信号を出す
-・筋トレは、発電所の置き場所を広げる
+✅ 筋トレは、発電所の置き場所を広げる
 筋トレだけ役割が違います。発電所をいくら建てても、置く場所がなければ増えないからです。
 だから問うべきは「どれが一番いいか」ではなく「自分に何が足りていないか」でした。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 目安も書きます。
 有酸素は中くらいの強さで週</t>
     </r>
@@ -29448,7 +29427,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">日以上。スクワットと腕立てで足ります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして始める順番があります。
 歩く、筋トレ、それから強度。
 私はこれを逆にやって失敗しました。</t>
@@ -29540,8 +29519,8 @@
       </rPr>
       <t xml:space="preserve">週間で終わった計画より、半年続いた計画のほうが強いです。
 適応は休んでいるあいだに起きます。睡眠を削って運動時間を作るのは、最悪の交換です。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -30048,12 +30027,12 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">とにかく疲れが抜けない。階段で息が切れる。手足が冷たい。
+      <t xml:space="preserve">🩸 とにかく疲れが抜けない。階段で息が切れる。手足が冷たい。
 でも健康診断は「貧血ではない」。
 だから気のせいかと思う。
 ここに落とし穴があります。
 貧血になる前の段階で、すでに不調は出ます。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 貧血の診断は血の濃さで決まりますが、体の中の鉄の蓄えは、その前から減っていきます。
 蓄えが空でも血の濃さは保たれている時期が、けっこう長いんです。
 そして鉄の役割は</t>
@@ -30077,17 +30056,17 @@
 酸素を運ぶ物質の中心にあること。そしてミトコンドリアの発電工程の部品であること。
 つまり足りないと、酸素が届かないうえに、届いた酸素を使う装置も動きにくくなります。配送が止まって、工場の機械も止まる。
 だから鉄不足の疲れは、寝ても抜けません。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 見るのはフェリチンという項目です。
 健康診断に入っていないことが多いので、医師に伝える必要があります。
-ーーーーー
+┈┈┈┈┈┈┈┈┈┈
 そして、ここは譲れない話です。
 自己判断でサプリを飲み続けないでください。
 鉄は捨てるしくみがほとんどなく、溜まると臓器に負担をかけます。
 そして貧血の原因は鉄不足だけではないです。どこかから出血している場合があり、サプリで数値だけ戻すと発見が遅れます。
 検査が先で、サプリは後です。
-全文はプロフィールのリンクから読めます。
-あとで見返すなら、保存してどうぞ。
+🔗 全文はプロフィールのリンクから読めます。
+📌 あとで見返すなら、保存してどうぞ。
 </t>
     </r>
     <r>
@@ -31232,65 +31211,7 @@
     <t xml:space="preserve">フック</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">冒頭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">125</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">字で「続きを読む」に折られるため、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">行目を</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">125</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">字以内にしています。</t>
-    </r>
+    <t xml:space="preserve">冒頭125字で「続きを読む」に折られるため、1行目を125字以内にしています。</t>
   </si>
   <si>
     <t xml:space="preserve">リンク</t>
@@ -31302,101 +31223,228 @@
     <t xml:space="preserve">ハッシュタグ</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">共通</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">個＋記事固有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">個＝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">個。重複がないことを検証済みです。</t>
-    </r>
+    <t xml:space="preserve">共通16個＋記事固有14個＝30個。重複がないことを検証済みです。</t>
   </si>
   <si>
     <t xml:space="preserve">タグの位置</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ピリオド</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">行の下に置いています。表示上、本文と分かれて見えます。</t>
-    </r>
+    <t xml:space="preserve">ピリオド3行の下に置いています。表示上、本文と分かれて見えます。</t>
   </si>
   <si>
     <t xml:space="preserve">絵文字</t>
   </si>
   <si>
-    <t xml:space="preserve">筆者ルールの口調に合わせて使っていません。必要なら追加できます。</t>
+    <t xml:space="preserve">役割のある位置にのみ使用。テーマ絵文字・箇条書き・要点・注意・リンク・保存の6種類です。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">■ 絵文字の凡例（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Instagram</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">版）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">記事のテーマを表す絵文字。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本すべて別のものを割り当てています。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">✅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">やることの箇条書き。元の「・」を置き換えたものです。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">💡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その記事の要点。「やることは」「対策は」で始まる行に付けています。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠️</t>
+  </si>
+  <si>
+    <t xml:space="preserve">注意・危険・受診に関わる行。危険、避けて、主治医などの語を含む場合。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">👉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">勧めの行。注意ではなく「相談してみてください」などの誘導に使います。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔗 📌</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">リンク案内と保存の誘導。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Instagram</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">はキャプション内のリンクが押せないため。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">┈┈┈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">区切り線。元の「ーーーーー」を見やすい記号に変えています。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">使用数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">投稿あたり種類で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個、平均</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">種類。装飾目的の連打はしていません。</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -31571,7 +31619,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -31668,12 +31716,16 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -33028,8 +33080,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
   </cols>
   <sheetData>
@@ -33056,7 +33107,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="n">
         <v>1</v>
       </c>
@@ -33068,19 +33119,19 @@
       </c>
       <c r="D2" s="14" t="n">
         <f aca="false">LEN(C2)</f>
-        <v>604</v>
+        <v>626</v>
       </c>
       <c r="E2" s="14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2" s="14" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G2" s="16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
         <v>2</v>
       </c>
@@ -33092,19 +33143,19 @@
       </c>
       <c r="D3" s="8" t="n">
         <f aca="false">LEN(C3)</f>
-        <v>648</v>
+        <v>666</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="n">
         <v>3</v>
       </c>
@@ -33116,19 +33167,19 @@
       </c>
       <c r="D4" s="14" t="n">
         <f aca="false">LEN(C4)</f>
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G4" s="16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
@@ -33140,19 +33191,19 @@
       </c>
       <c r="D5" s="8" t="n">
         <f aca="false">LEN(C5)</f>
-        <v>683</v>
+        <v>701</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="n">
         <v>5</v>
       </c>
@@ -33164,19 +33215,19 @@
       </c>
       <c r="D6" s="14" t="n">
         <f aca="false">LEN(C6)</f>
-        <v>678</v>
+        <v>701</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G6" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
         <v>6</v>
       </c>
@@ -33188,19 +33239,19 @@
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">LEN(C7)</f>
-        <v>713</v>
+        <v>743</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="n">
         <v>7</v>
       </c>
@@ -33212,19 +33263,19 @@
       </c>
       <c r="D8" s="14" t="n">
         <f aca="false">LEN(C8)</f>
-        <v>733</v>
+        <v>749</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G8" s="16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
         <v>8</v>
       </c>
@@ -33236,19 +33287,19 @@
       </c>
       <c r="D9" s="8" t="n">
         <f aca="false">LEN(C9)</f>
-        <v>722</v>
+        <v>738</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="n">
         <v>9</v>
       </c>
@@ -33260,19 +33311,19 @@
       </c>
       <c r="D10" s="14" t="n">
         <f aca="false">LEN(C10)</f>
-        <v>736</v>
+        <v>769</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G10" s="16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
         <v>10</v>
       </c>
@@ -33284,19 +33335,19 @@
       </c>
       <c r="D11" s="8" t="n">
         <f aca="false">LEN(C11)</f>
-        <v>740</v>
+        <v>769</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="n">
         <v>11</v>
       </c>
@@ -33308,19 +33359,19 @@
       </c>
       <c r="D12" s="14" t="n">
         <f aca="false">LEN(C12)</f>
-        <v>751</v>
+        <v>780</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G12" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
         <v>12</v>
       </c>
@@ -33332,19 +33383,19 @@
       </c>
       <c r="D13" s="8" t="n">
         <f aca="false">LEN(C13)</f>
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="n">
         <v>13</v>
       </c>
@@ -33356,19 +33407,19 @@
       </c>
       <c r="D14" s="14" t="n">
         <f aca="false">LEN(C14)</f>
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G14" s="16" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
         <v>14</v>
       </c>
@@ -33380,19 +33431,19 @@
       </c>
       <c r="D15" s="8" t="n">
         <f aca="false">LEN(C15)</f>
-        <v>761</v>
+        <v>786</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="n">
         <v>15</v>
       </c>
@@ -33404,19 +33455,19 @@
       </c>
       <c r="D16" s="14" t="n">
         <f aca="false">LEN(C16)</f>
-        <v>769</v>
+        <v>792</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G16" s="16" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
         <v>16</v>
       </c>
@@ -33428,19 +33479,19 @@
       </c>
       <c r="D17" s="8" t="n">
         <f aca="false">LEN(C17)</f>
-        <v>773</v>
+        <v>796</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="n">
         <v>17</v>
       </c>
@@ -33452,19 +33503,19 @@
       </c>
       <c r="D18" s="14" t="n">
         <f aca="false">LEN(C18)</f>
-        <v>781</v>
+        <v>811</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G18" s="16" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
         <v>18</v>
       </c>
@@ -33476,19 +33527,19 @@
       </c>
       <c r="D19" s="8" t="n">
         <f aca="false">LEN(C19)</f>
-        <v>755</v>
+        <v>776</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="n">
         <v>19</v>
       </c>
@@ -33500,19 +33551,19 @@
       </c>
       <c r="D20" s="14" t="n">
         <f aca="false">LEN(C20)</f>
-        <v>775</v>
+        <v>802</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
         <v>20</v>
       </c>
@@ -33524,19 +33575,19 @@
       </c>
       <c r="D21" s="8" t="n">
         <f aca="false">LEN(C21)</f>
-        <v>787</v>
+        <v>819</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="n">
         <v>21</v>
       </c>
@@ -33548,19 +33599,19 @@
       </c>
       <c r="D22" s="14" t="n">
         <f aca="false">LEN(C22)</f>
-        <v>800</v>
+        <v>832</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
         <v>22</v>
       </c>
@@ -33572,19 +33623,19 @@
       </c>
       <c r="D23" s="8" t="n">
         <f aca="false">LEN(C23)</f>
-        <v>791</v>
+        <v>819</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="n">
         <v>23</v>
       </c>
@@ -33596,19 +33647,19 @@
       </c>
       <c r="D24" s="14" t="n">
         <f aca="false">LEN(C24)</f>
-        <v>812</v>
+        <v>833</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G24" s="16" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
         <v>24</v>
       </c>
@@ -33620,19 +33671,19 @@
       </c>
       <c r="D25" s="8" t="n">
         <f aca="false">LEN(C25)</f>
-        <v>791</v>
+        <v>815</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G25" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="n">
         <v>25</v>
       </c>
@@ -33644,19 +33695,19 @@
       </c>
       <c r="D26" s="14" t="n">
         <f aca="false">LEN(C26)</f>
-        <v>788</v>
+        <v>807</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
         <v>26</v>
       </c>
@@ -33668,19 +33719,19 @@
       </c>
       <c r="D27" s="8" t="n">
         <f aca="false">LEN(C27)</f>
-        <v>812</v>
+        <v>837</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F27" s="8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="n">
         <v>27</v>
       </c>
@@ -33692,19 +33743,19 @@
       </c>
       <c r="D28" s="14" t="n">
         <f aca="false">LEN(C28)</f>
-        <v>772</v>
+        <v>792</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G28" s="16" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
         <v>28</v>
       </c>
@@ -33716,19 +33767,19 @@
       </c>
       <c r="D29" s="8" t="n">
         <f aca="false">LEN(C29)</f>
-        <v>787</v>
+        <v>811</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F29" s="8" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="n">
         <v>29</v>
       </c>
@@ -33740,19 +33791,19 @@
       </c>
       <c r="D30" s="14" t="n">
         <f aca="false">LEN(C30)</f>
-        <v>826</v>
+        <v>859</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G30" s="16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
         <v>30</v>
       </c>
@@ -33764,19 +33815,19 @@
       </c>
       <c r="D31" s="8" t="n">
         <f aca="false">LEN(C31)</f>
-        <v>804</v>
+        <v>828</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G31" s="11" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="n">
         <v>31</v>
       </c>
@@ -33788,19 +33839,19 @@
       </c>
       <c r="D32" s="14" t="n">
         <f aca="false">LEN(C32)</f>
-        <v>801</v>
+        <v>822</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G32" s="16" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
         <v>32</v>
       </c>
@@ -33812,19 +33863,19 @@
       </c>
       <c r="D33" s="8" t="n">
         <f aca="false">LEN(C33)</f>
-        <v>801</v>
+        <v>822</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="n">
         <v>33</v>
       </c>
@@ -33836,19 +33887,19 @@
       </c>
       <c r="D34" s="14" t="n">
         <f aca="false">LEN(C34)</f>
-        <v>810</v>
+        <v>833</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G34" s="16" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
         <v>34</v>
       </c>
@@ -33860,19 +33911,19 @@
       </c>
       <c r="D35" s="8" t="n">
         <f aca="false">LEN(C35)</f>
-        <v>834</v>
+        <v>858</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F35" s="8" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G35" s="11" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="259.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="n">
         <v>35</v>
       </c>
@@ -33884,13 +33935,13 @@
       </c>
       <c r="D36" s="14" t="n">
         <f aca="false">LEN(C36)</f>
-        <v>791</v>
+        <v>812</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="G36" s="16" t="s">
         <v>182</v>
@@ -33914,7 +33965,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
@@ -34082,7 +34133,7 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19"/>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="21" t="s">
         <v>255</v>
       </c>
       <c r="C22" s="20" t="s">
@@ -34091,7 +34142,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="19"/>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="21" t="s">
         <v>257</v>
       </c>
       <c r="C23" s="20" t="s">
@@ -34100,47 +34151,126 @@
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="19"/>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="22" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="19"/>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="22" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19"/>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="22" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="19"/>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="22" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="19"/>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="C28" s="25" t="s">
+      <c r="C28" s="22" t="s">
         <v>268</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="19"/>
+      <c r="B31" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="19"/>
+      <c r="B32" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="19"/>
+      <c r="B33" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="19"/>
+      <c r="B34" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="19"/>
+      <c r="B36" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="19"/>
+      <c r="B37" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="19"/>
+      <c r="B38" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
